--- a/Integration Quality/EMPRESAS/Relatorio - KONTIK BUSINESS TRAVEL.xlsx
+++ b/Integration Quality/EMPRESAS/Relatorio - KONTIK BUSINESS TRAVEL.xlsx
@@ -906,12 +906,12 @@
       <c r="E3" s="6" t="n">
         <v>45839.75217592593</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1095,12 +1095,12 @@
       <c r="E4" s="6" t="n">
         <v>45839.75162037037</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1284,12 +1284,12 @@
       <c r="E5" s="6" t="n">
         <v>45839.7472337963</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1475,12 +1475,12 @@
       <c r="E6" s="6" t="n">
         <v>45833.69987268518</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1666,12 +1666,12 @@
       <c r="E7" s="6" t="n">
         <v>45833.70637731482</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1857,12 +1857,12 @@
       <c r="E8" s="6" t="n">
         <v>45833.70702546297</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -2430,12 +2430,12 @@
       <c r="E11" s="6" t="n">
         <v>45845.25424768519</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -3956,12 +3956,12 @@
       <c r="E19" s="6" t="n">
         <v>45845.2852199074</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -4145,14 +4145,14 @@
       <c r="E20" s="6" t="n">
         <v>45845.25371527778</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -4336,14 +4336,14 @@
       <c r="E21" s="6" t="n">
         <v>45845.25712962963</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -5287,14 +5287,14 @@
       <c r="E26" s="6" t="n">
         <v>45842.51193287037</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -5478,14 +5478,14 @@
       <c r="E27" s="6" t="n">
         <v>45842.51193287037</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -5669,14 +5669,14 @@
       <c r="E28" s="6" t="n">
         <v>45839.78922453704</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -5858,14 +5858,14 @@
       <c r="E29" s="6" t="n">
         <v>45839.78922453704</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -6238,14 +6238,14 @@
       <c r="E31" s="6" t="n">
         <v>45845.25373842593</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -6429,14 +6429,14 @@
       <c r="E32" s="6" t="n">
         <v>45845.25372685185</v>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6620,14 +6620,14 @@
       <c r="E33" s="6" t="n">
         <v>45845.25712962963</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -6811,14 +6811,14 @@
       <c r="E34" s="6" t="n">
         <v>45845.25714120371</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -7002,14 +7002,14 @@
       <c r="E35" s="6" t="n">
         <v>45845.25714120371</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -7193,14 +7193,14 @@
       <c r="E36" s="6" t="n">
         <v>45845.25375</v>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -7384,14 +7384,14 @@
       <c r="E37" s="6" t="n">
         <v>45834.78646990741</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -7575,14 +7575,14 @@
       <c r="E38" s="6" t="n">
         <v>45838.55876157407</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -7768,14 +7768,14 @@
       <c r="E39" s="6" t="n">
         <v>45832.80255787037</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -7959,14 +7959,14 @@
       <c r="E40" s="6" t="n">
         <v>45837.25803240741</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -8148,14 +8148,14 @@
       <c r="E41" s="6" t="n">
         <v>45836.12898148148</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -8337,14 +8337,14 @@
       <c r="E42" s="6" t="n">
         <v>45838.60100694445</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -8526,14 +8526,14 @@
       <c r="E43" s="6" t="n">
         <v>45835.1358912037</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -8715,14 +8715,14 @@
       <c r="E44" s="6" t="n">
         <v>45835.13590277778</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -8904,14 +8904,14 @@
       <c r="E45" s="6" t="n">
         <v>45838.93004629629</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -9093,14 +9093,14 @@
       <c r="E46" s="6" t="n">
         <v>45842.51195601852</v>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -9284,14 +9284,14 @@
       <c r="E47" s="6" t="n">
         <v>45842.51197916667</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -9475,14 +9475,14 @@
       <c r="E48" s="6" t="n">
         <v>45842.51197916667</v>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -9666,14 +9666,14 @@
       <c r="E49" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -9857,14 +9857,14 @@
       <c r="E50" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -10048,14 +10048,14 @@
       <c r="E51" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -10239,14 +10239,14 @@
       <c r="E52" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -10430,14 +10430,14 @@
       <c r="E53" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -10621,14 +10621,14 @@
       <c r="E54" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -10812,14 +10812,14 @@
       <c r="E55" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -11003,14 +11003,14 @@
       <c r="E56" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -11194,14 +11194,14 @@
       <c r="E57" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -11385,14 +11385,14 @@
       <c r="E58" s="6" t="n">
         <v>45842.51194444444</v>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -11576,14 +11576,14 @@
       <c r="E59" s="6" t="n">
         <v>45840.67658564815</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -11765,14 +11765,14 @@
       <c r="E60" s="6" t="n">
         <v>45834.34078703704</v>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -11954,14 +11954,14 @@
       <c r="E61" s="6" t="n">
         <v>45838.92974537037</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -12145,14 +12145,14 @@
       <c r="E62" s="6" t="n">
         <v>45838.6281712963</v>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -12336,14 +12336,14 @@
       <c r="E63" s="6" t="n">
         <v>45838.61208333333</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -12527,14 +12527,14 @@
       <c r="E64" s="6" t="n">
         <v>45838.9297337963</v>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -12718,14 +12718,14 @@
       <c r="E65" s="6" t="n">
         <v>45834.86146990741</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -12911,14 +12911,14 @@
       <c r="E66" s="6" t="n">
         <v>45840.47699074074</v>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -13102,14 +13102,14 @@
       <c r="E67" s="6" t="n">
         <v>45833.86495370371</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -13291,14 +13291,14 @@
       <c r="E68" s="6" t="n">
         <v>45837.97599537037</v>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -13480,14 +13480,14 @@
       <c r="E69" s="6" t="n">
         <v>45835.54899305556</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -13669,14 +13669,14 @@
       <c r="E70" s="6" t="n">
         <v>45836.82009259259</v>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -13858,14 +13858,14 @@
       <c r="E71" s="6" t="n">
         <v>45838.93004629629</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -14047,14 +14047,14 @@
       <c r="E72" s="6" t="n">
         <v>45842.51201388889</v>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -14238,14 +14238,14 @@
       <c r="E73" s="6" t="n">
         <v>45835.45857638889</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -14431,14 +14431,14 @@
       <c r="E74" s="6" t="n">
         <v>45838.53185185185</v>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -14622,14 +14622,14 @@
       <c r="E75" s="6" t="n">
         <v>45842.51114583333</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -14815,14 +14815,14 @@
       <c r="E76" s="6" t="n">
         <v>45845.28516203703</v>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -15008,14 +15008,14 @@
       <c r="E77" s="6" t="n">
         <v>45832.72085648148</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -15199,14 +15199,14 @@
       <c r="E78" s="6" t="n">
         <v>45835.65068287037</v>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -15392,14 +15392,14 @@
       <c r="E79" s="6" t="n">
         <v>45835.6553125</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -15585,14 +15585,14 @@
       <c r="E80" s="6" t="n">
         <v>45839.83081018519</v>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -15776,14 +15776,14 @@
       <c r="E81" s="6" t="n">
         <v>45842.51274305556</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -15969,14 +15969,14 @@
       <c r="E82" s="6" t="n">
         <v>45841.47128472223</v>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -16162,14 +16162,14 @@
       <c r="E83" s="6" t="n">
         <v>45841.47128472223</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -16355,14 +16355,14 @@
       <c r="E84" s="6" t="n">
         <v>45841.5042824074</v>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -16548,14 +16548,14 @@
       <c r="E85" s="6" t="n">
         <v>45841.54403935185</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -16739,14 +16739,14 @@
       <c r="E86" s="6" t="n">
         <v>45841.54569444444</v>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -16930,14 +16930,14 @@
       <c r="E87" s="6" t="n">
         <v>45841.54574074074</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -17121,14 +17121,14 @@
       <c r="E88" s="6" t="n">
         <v>45840.02181712963</v>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -17312,14 +17312,14 @@
       <c r="E89" s="6" t="n">
         <v>45841.55478009259</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -17505,14 +17505,14 @@
       <c r="E90" s="6" t="n">
         <v>45841.55478009259</v>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -17698,14 +17698,14 @@
       <c r="E91" s="6" t="n">
         <v>45845.25375</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -17889,14 +17889,14 @@
       <c r="E92" s="6" t="n">
         <v>45845.25376157407</v>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -18080,14 +18080,14 @@
       <c r="E93" s="6" t="n">
         <v>45845.25377314815</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -18271,14 +18271,14 @@
       <c r="E94" s="6" t="n">
         <v>45839.69471064815</v>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -18462,14 +18462,14 @@
       <c r="E95" s="6" t="n">
         <v>45839.69517361111</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
@@ -18653,14 +18653,14 @@
       <c r="E96" s="6" t="n">
         <v>45839.69521990741</v>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -18844,14 +18844,14 @@
       <c r="E97" s="6" t="n">
         <v>45839.69527777778</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -19035,14 +19035,14 @@
       <c r="E98" s="6" t="n">
         <v>45839.69541666667</v>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -19226,14 +19226,14 @@
       <c r="E99" s="6" t="n">
         <v>45839.69988425926</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -19417,14 +19417,14 @@
       <c r="E100" s="6" t="n">
         <v>45840.70971064815</v>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -19608,14 +19608,14 @@
       <c r="E101" s="6" t="n">
         <v>45839.94829861111</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -19799,14 +19799,14 @@
       <c r="E102" s="6" t="n">
         <v>45841.46952546296</v>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -19990,14 +19990,14 @@
       <c r="E103" s="6" t="n">
         <v>45841.46959490741</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -20181,14 +20181,14 @@
       <c r="E104" s="6" t="n">
         <v>45840.5391087963</v>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -20372,14 +20372,14 @@
       <c r="E105" s="6" t="n">
         <v>45840.82724537037</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -20563,14 +20563,14 @@
       <c r="E106" s="6" t="n">
         <v>45842.51273148148</v>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -20756,14 +20756,14 @@
       <c r="E107" s="6" t="n">
         <v>45842.51273148148</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -20949,14 +20949,14 @@
       <c r="E108" s="6" t="n">
         <v>45842.5128125</v>
       </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -21142,14 +21142,14 @@
       <c r="E109" s="6" t="n">
         <v>45839.79633101852</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -21333,14 +21333,14 @@
       <c r="E110" s="6" t="n">
         <v>45845.25431712963</v>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -21524,14 +21524,14 @@
       <c r="E111" s="6" t="n">
         <v>45840.71327546296</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -21715,14 +21715,14 @@
       <c r="E112" s="6" t="n">
         <v>45841.62947916667</v>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -21906,14 +21906,14 @@
       <c r="E113" s="6" t="n">
         <v>45841.62989583334</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -22097,14 +22097,14 @@
       <c r="E114" s="6" t="n">
         <v>45841.50872685185</v>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -22288,14 +22288,14 @@
       <c r="E115" s="6" t="n">
         <v>45839.78618055556</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -22479,14 +22479,14 @@
       <c r="E116" s="6" t="n">
         <v>45839.26430555555</v>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -22670,14 +22670,14 @@
       <c r="E117" s="6" t="n">
         <v>45840.51524305555</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -22861,14 +22861,14 @@
       <c r="E118" s="6" t="n">
         <v>45841.62996527777</v>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -23052,14 +23052,14 @@
       <c r="E119" s="6" t="n">
         <v>45841.62960648148</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
@@ -23243,14 +23243,14 @@
       <c r="E120" s="6" t="n">
         <v>45840.62577546296</v>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -23434,14 +23434,14 @@
       <c r="E121" s="6" t="n">
         <v>45840.62578703704</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -23625,14 +23625,14 @@
       <c r="E122" s="6" t="n">
         <v>45845.2546412037</v>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -23816,14 +23816,14 @@
       <c r="E123" s="6" t="n">
         <v>45845.25424768519</v>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -24007,14 +24007,14 @@
       <c r="E124" s="6" t="n">
         <v>45845.25424768519</v>
       </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -24198,14 +24198,14 @@
       <c r="E125" s="6" t="n">
         <v>45841.48771990741</v>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -24389,14 +24389,14 @@
       <c r="E126" s="6" t="n">
         <v>45841.53747685185</v>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -24580,14 +24580,14 @@
       <c r="E127" s="6" t="n">
         <v>45839.53199074074</v>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -24771,14 +24771,14 @@
       <c r="E128" s="6" t="n">
         <v>45840.01490740741</v>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -24962,14 +24962,14 @@
       <c r="E129" s="6" t="n">
         <v>45839.79902777778</v>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -25153,14 +25153,14 @@
       <c r="E130" s="6" t="n">
         <v>45840.80962962963</v>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -25344,14 +25344,14 @@
       <c r="E131" s="6" t="n">
         <v>45839.52894675926</v>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -25535,14 +25535,14 @@
       <c r="E132" s="6" t="n">
         <v>45839.78975694445</v>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -25726,14 +25726,14 @@
       <c r="E133" s="6" t="n">
         <v>45840.51829861111</v>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -25917,14 +25917,14 @@
       <c r="E134" s="6" t="n">
         <v>45840.51829861111</v>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -26108,14 +26108,14 @@
       <c r="E135" s="6" t="n">
         <v>45845.25378472222</v>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -26299,14 +26299,14 @@
       <c r="E136" s="6" t="n">
         <v>45841.55303240741</v>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
@@ -26490,14 +26490,14 @@
       <c r="E137" s="6" t="n">
         <v>45839.05996527777</v>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -26681,14 +26681,14 @@
       <c r="E138" s="6" t="n">
         <v>45839.06377314815</v>
       </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -26872,14 +26872,14 @@
       <c r="E139" s="6" t="n">
         <v>45840.5432175926</v>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -27063,14 +27063,14 @@
       <c r="E140" s="6" t="n">
         <v>45840.02859953704</v>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -27254,14 +27254,14 @@
       <c r="E141" s="6" t="n">
         <v>45840.02871527777</v>
       </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -27445,14 +27445,14 @@
       <c r="E142" s="6" t="n">
         <v>45839.80938657407</v>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -27636,14 +27636,14 @@
       <c r="E143" s="6" t="n">
         <v>45839.75376157407</v>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -27827,14 +27827,14 @@
       <c r="E144" s="6" t="n">
         <v>45839.78965277778</v>
       </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -28018,14 +28018,14 @@
       <c r="E145" s="6" t="n">
         <v>45840.27864583334</v>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -28209,14 +28209,14 @@
       <c r="E146" s="6" t="n">
         <v>45840.79554398148</v>
       </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -28400,14 +28400,14 @@
       <c r="E147" s="6" t="n">
         <v>45839.79428240741</v>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -28591,14 +28591,14 @@
       <c r="E148" s="6" t="n">
         <v>45839.41907407407</v>
       </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -28784,14 +28784,14 @@
       <c r="E149" s="6" t="n">
         <v>45839.74636574074</v>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -28977,14 +28977,14 @@
       <c r="E150" s="6" t="n">
         <v>45839.40627314815</v>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -29170,14 +29170,14 @@
       <c r="E151" s="6" t="n">
         <v>45840.55630787037</v>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -29363,14 +29363,14 @@
       <c r="E152" s="6" t="n">
         <v>45840.5628125</v>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -29556,14 +29556,14 @@
       <c r="E153" s="6" t="n">
         <v>45840.36283564815</v>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -29749,14 +29749,14 @@
       <c r="E154" s="6" t="n">
         <v>45840.44391203704</v>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
@@ -29942,14 +29942,14 @@
       <c r="E155" s="6" t="n">
         <v>45840.45662037037</v>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -30135,14 +30135,14 @@
       <c r="E156" s="6" t="n">
         <v>45840.45663194444</v>
       </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -30328,14 +30328,14 @@
       <c r="E157" s="6" t="n">
         <v>45840.45664351852</v>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -30521,14 +30521,14 @@
       <c r="E158" s="6" t="n">
         <v>45840.47030092592</v>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
@@ -30714,14 +30714,14 @@
       <c r="E159" s="6" t="n">
         <v>45840.4703125</v>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -30907,14 +30907,14 @@
       <c r="E160" s="6" t="n">
         <v>45841.39392361111</v>
       </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -31100,14 +31100,14 @@
       <c r="E161" s="6" t="n">
         <v>45841.43811342592</v>
       </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -31293,14 +31293,14 @@
       <c r="E162" s="6" t="n">
         <v>45841.6691087963</v>
       </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
@@ -31486,14 +31486,14 @@
       <c r="E163" s="6" t="n">
         <v>45839.46883101852</v>
       </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -31679,14 +31679,14 @@
       <c r="E164" s="6" t="n">
         <v>45841.56305555555</v>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -31872,14 +31872,14 @@
       <c r="E165" s="6" t="n">
         <v>45841.56896990741</v>
       </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G165" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -32065,14 +32065,14 @@
       <c r="E166" s="6" t="n">
         <v>45841.56896990741</v>
       </c>
-      <c r="F166" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G166" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
@@ -32258,14 +32258,14 @@
       <c r="E167" s="6" t="n">
         <v>45839.26107638889</v>
       </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G167" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -32449,14 +32449,14 @@
       <c r="E168" s="6" t="n">
         <v>45839.77284722222</v>
       </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -32640,14 +32640,14 @@
       <c r="E169" s="6" t="n">
         <v>45839.77462962963</v>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -32831,14 +32831,14 @@
       <c r="E170" s="6" t="n">
         <v>45839.77462962963</v>
       </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G170" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -33022,14 +33022,14 @@
       <c r="E171" s="6" t="n">
         <v>45841.51817129629</v>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -33213,14 +33213,14 @@
       <c r="E172" s="6" t="n">
         <v>45841.01862268519</v>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -33404,14 +33404,14 @@
       <c r="E173" s="6" t="n">
         <v>45841.53362268519</v>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G173" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -33595,14 +33595,14 @@
       <c r="E174" s="6" t="n">
         <v>45839.79314814815</v>
       </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G174" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -33786,14 +33786,14 @@
       <c r="E175" s="6" t="n">
         <v>45840.01194444444</v>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -33977,14 +33977,14 @@
       <c r="E176" s="6" t="n">
         <v>45839.85664351852</v>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -34166,14 +34166,14 @@
       <c r="E177" s="6" t="n">
         <v>45838.89310185185</v>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -34355,14 +34355,14 @@
       <c r="E178" s="6" t="n">
         <v>45838.87592592592</v>
       </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -34544,14 +34544,14 @@
       <c r="E179" s="6" t="n">
         <v>45840.51269675926</v>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -34733,14 +34733,14 @@
       <c r="E180" s="6" t="n">
         <v>45840.78414351852</v>
       </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -34922,14 +34922,14 @@
       <c r="E181" s="6" t="n">
         <v>45840.51303240741</v>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -35111,14 +35111,14 @@
       <c r="E182" s="6" t="n">
         <v>45842.51203703704</v>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
@@ -35302,14 +35302,14 @@
       <c r="E183" s="6" t="n">
         <v>45842.51203703704</v>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -35493,14 +35493,14 @@
       <c r="E184" s="6" t="n">
         <v>45842.51203703704</v>
       </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
@@ -35684,14 +35684,14 @@
       <c r="E185" s="6" t="n">
         <v>45840.52177083334</v>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -35873,14 +35873,14 @@
       <c r="E186" s="6" t="n">
         <v>45840.01428240741</v>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -36062,14 +36062,14 @@
       <c r="E187" s="6" t="n">
         <v>45842.51210648148</v>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -36253,14 +36253,14 @@
       <c r="E188" s="6" t="n">
         <v>45841.01465277778</v>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
@@ -36442,14 +36442,14 @@
       <c r="E189" s="6" t="n">
         <v>45841.51947916667</v>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -36631,14 +36631,14 @@
       <c r="E190" s="6" t="n">
         <v>45842.51201388889</v>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -36822,14 +36822,14 @@
       <c r="E191" s="6" t="n">
         <v>45842.51201388889</v>
       </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -37013,14 +37013,14 @@
       <c r="E192" s="6" t="n">
         <v>45842.51201388889</v>
       </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -37204,14 +37204,14 @@
       <c r="E193" s="6" t="n">
         <v>45840.94854166666</v>
       </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G193" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -37393,14 +37393,14 @@
       <c r="E194" s="6" t="n">
         <v>45839.50744212963</v>
       </c>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G194" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -37582,14 +37582,14 @@
       <c r="E195" s="6" t="n">
         <v>45840.65332175926</v>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -37771,14 +37771,14 @@
       <c r="E196" s="6" t="n">
         <v>45840.65329861111</v>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -37960,14 +37960,14 @@
       <c r="E197" s="6" t="n">
         <v>45839.00387731481</v>
       </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -38151,14 +38151,14 @@
       <c r="E198" s="6" t="n">
         <v>45841.56896990741</v>
       </c>
-      <c r="F198" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G198" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -38344,14 +38344,14 @@
       <c r="E199" s="6" t="n">
         <v>45840.47998842593</v>
       </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -38533,14 +38533,14 @@
       <c r="E200" s="6" t="n">
         <v>45842.51206018519</v>
       </c>
-      <c r="F200" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -38724,14 +38724,14 @@
       <c r="E201" s="6" t="n">
         <v>45842.51207175926</v>
       </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -38915,14 +38915,14 @@
       <c r="E202" s="6" t="n">
         <v>45842.51207175926</v>
       </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -39106,14 +39106,14 @@
       <c r="E203" s="6" t="n">
         <v>45839.83706018519</v>
       </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G203" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -39295,14 +39295,14 @@
       <c r="E204" s="6" t="n">
         <v>45840.76864583333</v>
       </c>
-      <c r="F204" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G204" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -39484,14 +39484,14 @@
       <c r="E205" s="6" t="n">
         <v>45839.65329861111</v>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -39675,14 +39675,14 @@
       <c r="E206" s="6" t="n">
         <v>45838.90076388889</v>
       </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
@@ -39864,14 +39864,14 @@
       <c r="E207" s="6" t="n">
         <v>45840.51796296296</v>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -40053,14 +40053,14 @@
       <c r="E208" s="6" t="n">
         <v>45840.01438657408</v>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
@@ -40242,14 +40242,14 @@
       <c r="E209" s="6" t="n">
         <v>45839.85665509259</v>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
@@ -40431,14 +40431,14 @@
       <c r="E210" s="6" t="n">
         <v>45839.85673611111</v>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -40620,14 +40620,14 @@
       <c r="E211" s="6" t="n">
         <v>45840.79946759259</v>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
@@ -40809,14 +40809,14 @@
       <c r="E212" s="6" t="n">
         <v>45840.5453587963</v>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -41000,14 +41000,14 @@
       <c r="E213" s="6" t="n">
         <v>45840.81987268518</v>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -41189,14 +41189,14 @@
       <c r="E214" s="6" t="n">
         <v>45841.56896990741</v>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -41382,14 +41382,14 @@
       <c r="E215" s="6" t="n">
         <v>45840.4803125</v>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -41571,14 +41571,14 @@
       <c r="E216" s="6" t="n">
         <v>45839.7307175926</v>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -41760,14 +41760,14 @@
       <c r="E217" s="6" t="n">
         <v>45840.65331018518</v>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -41949,14 +41949,14 @@
       <c r="E218" s="6" t="n">
         <v>45840.82336805556</v>
       </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -42138,14 +42138,14 @@
       <c r="E219" s="6" t="n">
         <v>45840.74706018518</v>
       </c>
-      <c r="F219" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -42327,14 +42327,14 @@
       <c r="E220" s="6" t="n">
         <v>45840.66986111111</v>
       </c>
-      <c r="F220" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -42516,14 +42516,14 @@
       <c r="E221" s="6" t="n">
         <v>45840.66119212963</v>
       </c>
-      <c r="F221" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -42705,14 +42705,14 @@
       <c r="E222" s="6" t="n">
         <v>45840.81986111111</v>
       </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G222" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -42894,14 +42894,14 @@
       <c r="E223" s="6" t="n">
         <v>45841.6691087963</v>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H223" s="5" t="inlineStr">
@@ -43087,14 +43087,14 @@
       <c r="E224" s="6" t="n">
         <v>45839.55613425926</v>
       </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -43276,14 +43276,14 @@
       <c r="E225" s="6" t="n">
         <v>45839.77506944445</v>
       </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -43465,14 +43465,14 @@
       <c r="E226" s="6" t="n">
         <v>45841.56896990741</v>
       </c>
-      <c r="F226" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -43658,14 +43658,14 @@
       <c r="E227" s="6" t="n">
         <v>45840.47997685185</v>
       </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G227" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -43847,14 +43847,14 @@
       <c r="E228" s="6" t="n">
         <v>45840.35804398148</v>
       </c>
-      <c r="F228" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G228" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -44036,14 +44036,14 @@
       <c r="E229" s="6" t="n">
         <v>45841.35122685185</v>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -44225,14 +44225,14 @@
       <c r="E230" s="6" t="n">
         <v>45841.56896990741</v>
       </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -44418,14 +44418,14 @@
       <c r="E231" s="6" t="n">
         <v>45840.69484953704</v>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -44607,14 +44607,14 @@
       <c r="E232" s="6" t="n">
         <v>45840.75741898148</v>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -44796,14 +44796,14 @@
       <c r="E233" s="6" t="n">
         <v>45840.68457175926</v>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -44985,14 +44985,14 @@
       <c r="E234" s="6" t="n">
         <v>45840.54542824074</v>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -45174,14 +45174,14 @@
       <c r="E235" s="6" t="n">
         <v>45841.44837962963</v>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -45363,14 +45363,14 @@
       <c r="E236" s="6" t="n">
         <v>45838.75751157408</v>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
@@ -45554,14 +45554,14 @@
       <c r="E237" s="6" t="n">
         <v>45838.75751157408</v>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -45745,14 +45745,14 @@
       <c r="E238" s="6" t="n">
         <v>45842.92787037037</v>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -45936,14 +45936,14 @@
       <c r="E239" s="6" t="n">
         <v>45842.92868055555</v>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -46127,14 +46127,14 @@
       <c r="E240" s="6" t="n">
         <v>45842.83755787037</v>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -46318,14 +46318,14 @@
       <c r="E241" s="6" t="n">
         <v>45842.92916666667</v>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -46509,14 +46509,14 @@
       <c r="E242" s="6" t="n">
         <v>45842.93075231482</v>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -46700,14 +46700,14 @@
       <c r="E243" s="6" t="n">
         <v>45841.81983796296</v>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -46891,14 +46891,14 @@
       <c r="E244" s="6" t="n">
         <v>45842.81318287037</v>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -47082,14 +47082,14 @@
       <c r="E245" s="6" t="n">
         <v>45843.02467592592</v>
       </c>
-      <c r="F245" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G245" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -47273,14 +47273,14 @@
       <c r="E246" s="6" t="n">
         <v>45845.25715277778</v>
       </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G246" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
@@ -47464,14 +47464,14 @@
       <c r="E247" s="6" t="n">
         <v>45842.73696759259</v>
       </c>
-      <c r="F247" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G247" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -47655,14 +47655,14 @@
       <c r="E248" s="6" t="n">
         <v>45841.97577546296</v>
       </c>
-      <c r="F248" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G248" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -47846,14 +47846,14 @@
       <c r="E249" s="6" t="n">
         <v>45842.48349537037</v>
       </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G249" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -48037,14 +48037,14 @@
       <c r="E250" s="6" t="n">
         <v>45841.72491898148</v>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G250" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -48228,14 +48228,14 @@
       <c r="E251" s="6" t="n">
         <v>45841.72591435185</v>
       </c>
-      <c r="F251" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G251" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G251" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -48419,14 +48419,14 @@
       <c r="E252" s="6" t="n">
         <v>45845.25409722222</v>
       </c>
-      <c r="F252" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G252" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
@@ -48610,14 +48610,14 @@
       <c r="E253" s="6" t="n">
         <v>45842.73809027778</v>
       </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G253" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -48803,14 +48803,14 @@
       <c r="E254" s="6" t="n">
         <v>45842.73809027778</v>
       </c>
-      <c r="F254" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G254" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -48996,14 +48996,14 @@
       <c r="E255" s="6" t="n">
         <v>45842.53884259259</v>
       </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -49187,14 +49187,14 @@
       <c r="E256" s="6" t="n">
         <v>45845.2541087963</v>
       </c>
-      <c r="F256" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G256" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -49378,14 +49378,14 @@
       <c r="E257" s="6" t="n">
         <v>45842.5703125</v>
       </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G257" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F257" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G257" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -49569,14 +49569,14 @@
       <c r="E258" s="6" t="n">
         <v>45842.82680555555</v>
       </c>
-      <c r="F258" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G258" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F258" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
@@ -49760,14 +49760,14 @@
       <c r="E259" s="6" t="n">
         <v>45845.2541087963</v>
       </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G259" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
@@ -49951,14 +49951,14 @@
       <c r="E260" s="6" t="n">
         <v>45842.56278935185</v>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
@@ -50144,14 +50144,14 @@
       <c r="E261" s="6" t="n">
         <v>45842.56278935185</v>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G261" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -50337,14 +50337,14 @@
       <c r="E262" s="6" t="n">
         <v>45842.71922453704</v>
       </c>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G262" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -50530,14 +50530,14 @@
       <c r="E263" s="6" t="n">
         <v>45842.71930555555</v>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G263" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
@@ -50723,14 +50723,14 @@
       <c r="E264" s="6" t="n">
         <v>45841.70040509259</v>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
@@ -50916,14 +50916,14 @@
       <c r="E265" s="6" t="n">
         <v>45842.68143518519</v>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -51109,14 +51109,14 @@
       <c r="E266" s="6" t="n">
         <v>45842.61773148148</v>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F266" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
@@ -51302,14 +51302,14 @@
       <c r="E267" s="6" t="n">
         <v>45842.6377662037</v>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -51495,14 +51495,14 @@
       <c r="E268" s="6" t="n">
         <v>45842.73431712963</v>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -51688,14 +51688,14 @@
       <c r="E269" s="6" t="n">
         <v>45842.51292824074</v>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F269" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G269" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -51881,14 +51881,14 @@
       <c r="E270" s="6" t="n">
         <v>45842.75439814815</v>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F270" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G270" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -52074,14 +52074,14 @@
       <c r="E271" s="6" t="n">
         <v>45842.76306712963</v>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G271" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -52265,14 +52265,14 @@
       <c r="E272" s="6" t="n">
         <v>45842.76340277777</v>
       </c>
-      <c r="F272" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G272" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F272" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G272" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
@@ -52456,14 +52456,14 @@
       <c r="E273" s="6" t="n">
         <v>45845.25861111111</v>
       </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G273" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F273" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G273" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -52647,14 +52647,14 @@
       <c r="E274" s="6" t="n">
         <v>45845.25862268519</v>
       </c>
-      <c r="F274" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G274" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F274" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G274" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
@@ -52838,14 +52838,14 @@
       <c r="E275" s="6" t="n">
         <v>45842.59269675926</v>
       </c>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G275" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F275" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G275" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -53029,14 +53029,14 @@
       <c r="E276" s="6" t="n">
         <v>45842.67193287037</v>
       </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G276" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F276" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G276" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
@@ -53220,14 +53220,14 @@
       <c r="E277" s="6" t="n">
         <v>45842.71685185185</v>
       </c>
-      <c r="F277" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G277" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F277" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G277" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -53411,14 +53411,14 @@
       <c r="E278" s="6" t="n">
         <v>45842.71716435185</v>
       </c>
-      <c r="F278" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G278" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F278" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G278" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
@@ -53602,14 +53602,14 @@
       <c r="E279" s="6" t="n">
         <v>45842.71717592593</v>
       </c>
-      <c r="F279" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G279" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F279" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G279" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
@@ -53793,14 +53793,14 @@
       <c r="E280" s="6" t="n">
         <v>45842.7171875</v>
       </c>
-      <c r="F280" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G280" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F280" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G280" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
@@ -53984,14 +53984,14 @@
       <c r="E281" s="6" t="n">
         <v>45842.7171875</v>
       </c>
-      <c r="F281" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G281" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F281" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G281" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
@@ -54175,14 +54175,14 @@
       <c r="E282" s="6" t="n">
         <v>45842.71719907408</v>
       </c>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G282" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F282" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G282" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
@@ -54366,14 +54366,14 @@
       <c r="E283" s="6" t="n">
         <v>45842.71726851852</v>
       </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F283" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G283" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -54557,14 +54557,14 @@
       <c r="E284" s="6" t="n">
         <v>45842.71728009259</v>
       </c>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G284" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F284" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G284" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -54748,14 +54748,14 @@
       <c r="E285" s="6" t="n">
         <v>45842.52964120371</v>
       </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G285" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F285" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G285" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -54939,14 +54939,14 @@
       <c r="E286" s="6" t="n">
         <v>45842.5296875</v>
       </c>
-      <c r="F286" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G286" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F286" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G286" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
@@ -55130,14 +55130,14 @@
       <c r="E287" s="6" t="n">
         <v>45842.53476851852</v>
       </c>
-      <c r="F287" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G287" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F287" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G287" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -55321,14 +55321,14 @@
       <c r="E288" s="6" t="n">
         <v>45841.79347222222</v>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F288" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G288" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -55512,14 +55512,14 @@
       <c r="E289" s="6" t="n">
         <v>45841.79556712963</v>
       </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G289" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G289" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -55703,14 +55703,14 @@
       <c r="E290" s="6" t="n">
         <v>45845.25714120371</v>
       </c>
-      <c r="F290" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G290" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F290" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G290" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
@@ -55894,14 +55894,14 @@
       <c r="E291" s="6" t="n">
         <v>45845.25714120371</v>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G291" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F291" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G291" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
@@ -56085,14 +56085,14 @@
       <c r="E292" s="6" t="n">
         <v>45842.46319444444</v>
       </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G292" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F292" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G292" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
@@ -56276,14 +56276,14 @@
       <c r="E293" s="6" t="n">
         <v>45845.2587037037</v>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F293" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G293" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -56467,14 +56467,14 @@
       <c r="E294" s="6" t="n">
         <v>45845.25861111111</v>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F294" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G294" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -56658,14 +56658,14 @@
       <c r="E295" s="6" t="n">
         <v>45842.55300925926</v>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F295" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G295" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -56849,14 +56849,14 @@
       <c r="E296" s="6" t="n">
         <v>45841.81302083333</v>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F296" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G296" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
@@ -57040,14 +57040,14 @@
       <c r="E297" s="6" t="n">
         <v>45842.53884259259</v>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F297" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G297" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -57231,14 +57231,14 @@
       <c r="E298" s="6" t="n">
         <v>45845.2541087963</v>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F298" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G298" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -57422,14 +57422,14 @@
       <c r="E299" s="6" t="n">
         <v>45842.75369212963</v>
       </c>
-      <c r="F299" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G299" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F299" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G299" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
@@ -57613,14 +57613,14 @@
       <c r="E300" s="6" t="n">
         <v>45842.75372685185</v>
       </c>
-      <c r="F300" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G300" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F300" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G300" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -57804,14 +57804,14 @@
       <c r="E301" s="6" t="n">
         <v>45842.75380787037</v>
       </c>
-      <c r="F301" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G301" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F301" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G301" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -57995,14 +57995,14 @@
       <c r="E302" s="6" t="n">
         <v>45842.7859375</v>
       </c>
-      <c r="F302" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G302" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F302" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G302" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -58186,14 +58186,14 @@
       <c r="E303" s="6" t="n">
         <v>45842.64391203703</v>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G303" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -58379,14 +58379,14 @@
       <c r="E304" s="6" t="n">
         <v>45841.83715277778</v>
       </c>
-      <c r="F304" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G304" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F304" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G304" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -58570,14 +58570,14 @@
       <c r="E305" s="6" t="n">
         <v>45842.57053240741</v>
       </c>
-      <c r="F305" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G305" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F305" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G305" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -58761,14 +58761,14 @@
       <c r="E306" s="6" t="n">
         <v>45842.57395833333</v>
       </c>
-      <c r="F306" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G306" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F306" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G306" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
@@ -58952,14 +58952,14 @@
       <c r="E307" s="6" t="n">
         <v>45841.83405092593</v>
       </c>
-      <c r="F307" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G307" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F307" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G307" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -59143,14 +59143,14 @@
       <c r="E308" s="6" t="n">
         <v>45842.83012731482</v>
       </c>
-      <c r="F308" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G308" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F308" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G308" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
@@ -59334,14 +59334,14 @@
       <c r="E309" s="6" t="n">
         <v>45842.52619212963</v>
       </c>
-      <c r="F309" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G309" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F309" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G309" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -59527,14 +59527,14 @@
       <c r="E310" s="6" t="n">
         <v>45842.73440972222</v>
       </c>
-      <c r="F310" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G310" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F310" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G310" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -59720,14 +59720,14 @@
       <c r="E311" s="6" t="n">
         <v>45842.76274305556</v>
       </c>
-      <c r="F311" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G311" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F311" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G311" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -59913,14 +59913,14 @@
       <c r="E312" s="6" t="n">
         <v>45845.25715277778</v>
       </c>
-      <c r="F312" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G312" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F312" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G312" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
@@ -60104,14 +60104,14 @@
       <c r="E313" s="6" t="n">
         <v>45841.8065162037</v>
       </c>
-      <c r="F313" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G313" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F313" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G313" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
@@ -60295,14 +60295,14 @@
       <c r="E314" s="6" t="n">
         <v>45841.68157407407</v>
       </c>
-      <c r="F314" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G314" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F314" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G314" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -60488,14 +60488,14 @@
       <c r="E315" s="6" t="n">
         <v>45841.68162037037</v>
       </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F315" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G315" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -60681,14 +60681,14 @@
       <c r="E316" s="6" t="n">
         <v>45841.68763888889</v>
       </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F316" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G316" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
@@ -60874,14 +60874,14 @@
       <c r="E317" s="6" t="n">
         <v>45841.75633101852</v>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F317" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G317" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
@@ -61067,14 +61067,14 @@
       <c r="E318" s="6" t="n">
         <v>45841.75633101852</v>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F318" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G318" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
@@ -61260,14 +61260,14 @@
       <c r="E319" s="6" t="n">
         <v>45842.50034722222</v>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F319" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G319" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
@@ -61453,14 +61453,14 @@
       <c r="E320" s="6" t="n">
         <v>45842.48778935185</v>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F320" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G320" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
@@ -61646,14 +61646,14 @@
       <c r="E321" s="6" t="n">
         <v>45842.43780092592</v>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F321" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G321" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -61839,14 +61839,14 @@
       <c r="E322" s="6" t="n">
         <v>45842.44412037037</v>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F322" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G322" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
@@ -62032,14 +62032,14 @@
       <c r="E323" s="6" t="n">
         <v>45842.44412037037</v>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F323" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G323" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
@@ -62225,14 +62225,14 @@
       <c r="E324" s="6" t="n">
         <v>45842.43153935186</v>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F324" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G324" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
@@ -62418,14 +62418,14 @@
       <c r="E325" s="6" t="n">
         <v>45842.43155092592</v>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F325" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G325" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
@@ -62611,14 +62611,14 @@
       <c r="E326" s="6" t="n">
         <v>45842.43155092592</v>
       </c>
-      <c r="F326" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G326" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F326" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G326" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H326" s="5" t="inlineStr">
@@ -62804,14 +62804,14 @@
       <c r="E327" s="6" t="n">
         <v>45841.79418981481</v>
       </c>
-      <c r="F327" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G327" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F327" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G327" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
@@ -62997,14 +62997,14 @@
       <c r="E328" s="6" t="n">
         <v>45842.39383101852</v>
       </c>
-      <c r="F328" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G328" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F328" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G328" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H328" s="5" t="inlineStr">
@@ -63190,14 +63190,14 @@
       <c r="E329" s="6" t="n">
         <v>45842.40659722222</v>
       </c>
-      <c r="F329" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G329" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F329" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G329" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H329" s="5" t="inlineStr">
@@ -63383,14 +63383,14 @@
       <c r="E330" s="6" t="n">
         <v>45842.40659722222</v>
       </c>
-      <c r="F330" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G330" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F330" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G330" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H330" s="5" t="inlineStr">
@@ -63576,14 +63576,14 @@
       <c r="E331" s="6" t="n">
         <v>45842.40660879629</v>
       </c>
-      <c r="F331" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G331" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F331" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G331" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H331" s="5" t="inlineStr">
@@ -63769,14 +63769,14 @@
       <c r="E332" s="6" t="n">
         <v>45842.41299768518</v>
       </c>
-      <c r="F332" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G332" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F332" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G332" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H332" s="5" t="inlineStr">
@@ -63962,14 +63962,14 @@
       <c r="E333" s="6" t="n">
         <v>45842.41300925926</v>
       </c>
-      <c r="F333" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G333" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F333" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G333" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H333" s="5" t="inlineStr">
@@ -64155,14 +64155,14 @@
       <c r="E334" s="6" t="n">
         <v>45842.41302083333</v>
       </c>
-      <c r="F334" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G334" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F334" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G334" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H334" s="5" t="inlineStr">
@@ -64348,14 +64348,14 @@
       <c r="E335" s="6" t="n">
         <v>45842.70048611111</v>
       </c>
-      <c r="F335" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G335" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F335" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G335" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H335" s="5" t="inlineStr">
@@ -64541,14 +64541,14 @@
       <c r="E336" s="6" t="n">
         <v>45842.70049768518</v>
       </c>
-      <c r="F336" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G336" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F336" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G336" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H336" s="5" t="inlineStr">
@@ -64734,14 +64734,14 @@
       <c r="E337" s="6" t="n">
         <v>45842.53140046296</v>
       </c>
-      <c r="F337" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F337" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G337" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H337" s="5" t="inlineStr">
@@ -64927,14 +64927,14 @@
       <c r="E338" s="6" t="n">
         <v>45842.57509259259</v>
       </c>
-      <c r="F338" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G338" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F338" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G338" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H338" s="5" t="inlineStr">
@@ -65120,14 +65120,14 @@
       <c r="E339" s="6" t="n">
         <v>45842.76849537037</v>
       </c>
-      <c r="F339" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G339" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F339" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G339" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H339" s="5" t="inlineStr">
@@ -65311,14 +65311,14 @@
       <c r="E340" s="6" t="n">
         <v>45842.54540509259</v>
       </c>
-      <c r="F340" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G340" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F340" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G340" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
@@ -65502,14 +65502,14 @@
       <c r="E341" s="6" t="n">
         <v>45842.79560185185</v>
       </c>
-      <c r="F341" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G341" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F341" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G341" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H341" s="5" t="inlineStr">
@@ -65693,14 +65693,14 @@
       <c r="E342" s="6" t="n">
         <v>45842.53940972222</v>
       </c>
-      <c r="F342" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G342" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F342" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G342" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H342" s="5" t="inlineStr">
@@ -65884,14 +65884,14 @@
       <c r="E343" s="6" t="n">
         <v>45842.50458333334</v>
       </c>
-      <c r="F343" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G343" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F343" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G343" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H343" s="5" t="inlineStr">
@@ -66077,14 +66077,14 @@
       <c r="E344" s="6" t="n">
         <v>45843.23075231481</v>
       </c>
-      <c r="F344" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G344" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F344" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G344" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H344" s="5" t="inlineStr">
@@ -66268,14 +66268,14 @@
       <c r="E345" s="6" t="n">
         <v>45842.54435185185</v>
       </c>
-      <c r="F345" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G345" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F345" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G345" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
@@ -66457,14 +66457,14 @@
       <c r="E346" s="6" t="n">
         <v>45842.54436342593</v>
       </c>
-      <c r="F346" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G346" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F346" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G346" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H346" s="5" t="inlineStr">
@@ -66646,14 +66646,14 @@
       <c r="E347" s="6" t="n">
         <v>45842.54436342593</v>
       </c>
-      <c r="F347" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G347" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F347" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G347" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H347" s="5" t="inlineStr">
@@ -66835,14 +66835,14 @@
       <c r="E348" s="6" t="n">
         <v>45843.23741898148</v>
       </c>
-      <c r="F348" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G348" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F348" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G348" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H348" s="5" t="inlineStr">
@@ -67026,14 +67026,14 @@
       <c r="E349" s="6" t="n">
         <v>45842.93186342593</v>
       </c>
-      <c r="F349" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G349" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F349" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G349" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
@@ -67215,14 +67215,14 @@
       <c r="E350" s="6" t="n">
         <v>45842.85033564815</v>
       </c>
-      <c r="F350" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G350" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F350" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G350" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H350" s="5" t="inlineStr">
@@ -67406,14 +67406,14 @@
       <c r="E351" s="6" t="n">
         <v>45842.85033564815</v>
       </c>
-      <c r="F351" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G351" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F351" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G351" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H351" s="5" t="inlineStr">
@@ -67597,14 +67597,14 @@
       <c r="E352" s="6" t="n">
         <v>45842.85033564815</v>
       </c>
-      <c r="F352" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G352" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F352" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G352" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H352" s="5" t="inlineStr">
@@ -67788,14 +67788,14 @@
       <c r="E353" s="6" t="n">
         <v>45841.79322916667</v>
       </c>
-      <c r="F353" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G353" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F353" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G353" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
@@ -67977,14 +67977,14 @@
       <c r="E354" s="6" t="n">
         <v>45842.79387731481</v>
       </c>
-      <c r="F354" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G354" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F354" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G354" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H354" s="5" t="inlineStr">
@@ -68166,14 +68166,14 @@
       <c r="E355" s="6" t="n">
         <v>45843.02144675926</v>
       </c>
-      <c r="F355" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G355" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F355" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G355" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -68355,14 +68355,14 @@
       <c r="E356" s="6" t="n">
         <v>45843.02144675926</v>
       </c>
-      <c r="F356" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G356" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F356" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G356" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H356" s="5" t="inlineStr">
@@ -68544,14 +68544,14 @@
       <c r="E357" s="6" t="n">
         <v>45842.54006944445</v>
       </c>
-      <c r="F357" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G357" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F357" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G357" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -68733,14 +68733,14 @@
       <c r="E358" s="6" t="n">
         <v>45842.54006944445</v>
       </c>
-      <c r="F358" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G358" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F358" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G358" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H358" s="5" t="inlineStr">
@@ -68922,14 +68922,14 @@
       <c r="E359" s="6" t="n">
         <v>45842.76275462963</v>
       </c>
-      <c r="F359" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G359" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F359" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G359" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H359" s="5" t="inlineStr">
@@ -69113,14 +69113,14 @@
       <c r="E360" s="6" t="n">
         <v>45842.76275462963</v>
       </c>
-      <c r="F360" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G360" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F360" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G360" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H360" s="5" t="inlineStr">
@@ -69304,14 +69304,14 @@
       <c r="E361" s="6" t="n">
         <v>45842.51278935185</v>
       </c>
-      <c r="F361" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G361" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F361" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G361" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H361" s="5" t="inlineStr">
@@ -69495,14 +69495,14 @@
       <c r="E362" s="6" t="n">
         <v>45843.21126157408</v>
       </c>
-      <c r="F362" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G362" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F362" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G362" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H362" s="5" t="inlineStr">
@@ -69686,14 +69686,14 @@
       <c r="E363" s="6" t="n">
         <v>45841.51947916667</v>
       </c>
-      <c r="F363" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G363" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F363" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G363" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H363" s="5" t="inlineStr">
@@ -69875,14 +69875,14 @@
       <c r="E364" s="6" t="n">
         <v>45842.56545138889</v>
       </c>
-      <c r="F364" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G364" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F364" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G364" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H364" s="5" t="inlineStr">
@@ -70066,14 +70066,14 @@
       <c r="E365" s="6" t="n">
         <v>45842.85025462963</v>
       </c>
-      <c r="F365" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G365" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F365" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G365" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H365" s="5" t="inlineStr">
@@ -70257,14 +70257,14 @@
       <c r="E366" s="6" t="n">
         <v>45842.69746527778</v>
       </c>
-      <c r="F366" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G366" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F366" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G366" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H366" s="5" t="inlineStr">
@@ -70448,14 +70448,14 @@
       <c r="E367" s="6" t="n">
         <v>45842.69746527778</v>
       </c>
-      <c r="F367" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G367" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F367" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G367" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H367" s="5" t="inlineStr">
@@ -70639,14 +70639,14 @@
       <c r="E368" s="6" t="n">
         <v>45842.93399305556</v>
       </c>
-      <c r="F368" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G368" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F368" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G368" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H368" s="5" t="inlineStr">
@@ -70828,14 +70828,14 @@
       <c r="E369" s="6" t="n">
         <v>45842.85033564815</v>
       </c>
-      <c r="F369" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G369" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F369" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G369" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
@@ -71019,14 +71019,14 @@
       <c r="E370" s="6" t="n">
         <v>45842.85033564815</v>
       </c>
-      <c r="F370" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G370" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F370" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G370" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H370" s="5" t="inlineStr">
@@ -71210,14 +71210,14 @@
       <c r="E371" s="6" t="n">
         <v>45842.85033564815</v>
       </c>
-      <c r="F371" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G371" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F371" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G371" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H371" s="5" t="inlineStr">
@@ -71401,14 +71401,14 @@
       <c r="E372" s="6" t="n">
         <v>45842.74405092592</v>
       </c>
-      <c r="F372" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G372" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F372" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G372" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H372" s="5" t="inlineStr">
@@ -71592,14 +71592,14 @@
       <c r="E373" s="6" t="n">
         <v>45842.74405092592</v>
       </c>
-      <c r="F373" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G373" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F373" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G373" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H373" s="5" t="inlineStr">
@@ -71783,14 +71783,14 @@
       <c r="E374" s="6" t="n">
         <v>45842.8547337963</v>
       </c>
-      <c r="F374" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G374" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F374" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G374" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H374" s="5" t="inlineStr">
@@ -71974,14 +71974,14 @@
       <c r="E375" s="6" t="n">
         <v>45841.7158912037</v>
       </c>
-      <c r="F375" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G375" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F375" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G375" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -72163,14 +72163,14 @@
       <c r="E376" s="6" t="n">
         <v>45842.67106481481</v>
       </c>
-      <c r="F376" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G376" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F376" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G376" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H376" s="5" t="inlineStr">
@@ -72356,14 +72356,14 @@
       <c r="E377" s="6" t="n">
         <v>45842.68155092592</v>
       </c>
-      <c r="F377" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G377" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F377" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G377" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H377" s="5" t="inlineStr">
@@ -72549,14 +72549,14 @@
       <c r="E378" s="6" t="n">
         <v>45842.61773148148</v>
       </c>
-      <c r="F378" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G378" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F378" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G378" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H378" s="5" t="inlineStr">
@@ -72742,14 +72742,14 @@
       <c r="E379" s="6" t="n">
         <v>45841.67383101852</v>
       </c>
-      <c r="F379" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G379" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F379" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G379" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -72931,14 +72931,14 @@
       <c r="E380" s="6" t="n">
         <v>45841.68157407407</v>
       </c>
-      <c r="F380" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G380" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F380" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G380" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
@@ -73124,14 +73124,14 @@
       <c r="E381" s="6" t="n">
         <v>45842.64620370371</v>
       </c>
-      <c r="F381" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G381" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F381" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G381" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H381" s="5" t="inlineStr">
@@ -73317,14 +73317,14 @@
       <c r="E382" s="6" t="n">
         <v>45842.7678125</v>
       </c>
-      <c r="F382" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G382" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F382" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G382" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H382" s="5" t="inlineStr">
@@ -73508,14 +73508,14 @@
       <c r="E383" s="6" t="n">
         <v>45842.51267361111</v>
       </c>
-      <c r="F383" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G383" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F383" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G383" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H383" s="5" t="inlineStr">
@@ -73699,14 +73699,14 @@
       <c r="E384" s="6" t="n">
         <v>45842.73435185185</v>
       </c>
-      <c r="F384" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G384" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F384" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G384" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H384" s="5" t="inlineStr">
@@ -73892,14 +73892,14 @@
       <c r="E385" s="6" t="n">
         <v>45842.5128587963</v>
       </c>
-      <c r="F385" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G385" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F385" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G385" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H385" s="5" t="inlineStr">
@@ -74085,14 +74085,14 @@
       <c r="E386" s="6" t="n">
         <v>45841.6691087963</v>
       </c>
-      <c r="F386" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G386" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F386" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G386" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H386" s="5" t="inlineStr">
@@ -74278,14 +74278,14 @@
       <c r="E387" s="6" t="n">
         <v>45845.28517361111</v>
       </c>
-      <c r="F387" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G387" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F387" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G387" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H387" s="5" t="inlineStr">
@@ -74471,14 +74471,14 @@
       <c r="E388" s="6" t="n">
         <v>45841.68157407407</v>
       </c>
-      <c r="F388" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G388" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F388" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G388" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H388" s="5" t="inlineStr">
@@ -74664,14 +74664,14 @@
       <c r="E389" s="6" t="n">
         <v>45842.51290509259</v>
       </c>
-      <c r="F389" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G389" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F389" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G389" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H389" s="5" t="inlineStr">
@@ -74857,14 +74857,14 @@
       <c r="E390" s="6" t="n">
         <v>45842.29578703704</v>
       </c>
-      <c r="F390" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G390" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F390" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G390" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -75046,14 +75046,14 @@
       <c r="E391" s="6" t="n">
         <v>45842.29578703704</v>
       </c>
-      <c r="F391" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G391" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F391" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G391" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -75235,14 +75235,14 @@
       <c r="E392" s="6" t="n">
         <v>45842.29578703704</v>
       </c>
-      <c r="F392" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G392" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F392" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G392" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -75424,14 +75424,14 @@
       <c r="E393" s="6" t="n">
         <v>45842.2959375</v>
       </c>
-      <c r="F393" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G393" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F393" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G393" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -75613,14 +75613,14 @@
       <c r="E394" s="6" t="n">
         <v>45842.2959375</v>
       </c>
-      <c r="F394" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G394" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F394" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G394" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -75802,14 +75802,14 @@
       <c r="E395" s="6" t="n">
         <v>45842.65658564815</v>
       </c>
-      <c r="F395" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G395" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F395" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G395" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H395" s="5" t="inlineStr">
@@ -75995,14 +75995,14 @@
       <c r="E396" s="6" t="n">
         <v>45842.66270833334</v>
       </c>
-      <c r="F396" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G396" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F396" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G396" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H396" s="5" t="inlineStr">
@@ -76188,14 +76188,14 @@
       <c r="E397" s="6" t="n">
         <v>45842.73435185185</v>
       </c>
-      <c r="F397" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G397" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F397" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G397" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H397" s="5" t="inlineStr">
@@ -76381,14 +76381,14 @@
       <c r="E398" s="6" t="n">
         <v>45842.51283564815</v>
       </c>
-      <c r="F398" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G398" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F398" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G398" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H398" s="5" t="inlineStr">
@@ -76574,14 +76574,14 @@
       <c r="E399" s="6" t="n">
         <v>45843.42530092593</v>
       </c>
-      <c r="F399" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G399" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F399" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G399" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
@@ -76767,14 +76767,14 @@
       <c r="E400" s="6" t="n">
         <v>45845.00395833333</v>
       </c>
-      <c r="F400" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G400" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F400" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G400" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
         </is>
       </c>
       <c r="H400" s="5" t="inlineStr">
@@ -76958,14 +76958,14 @@
       <c r="E401" s="6" t="n">
         <v>45843.25376157407</v>
       </c>
-      <c r="F401" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G401" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F401" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G401" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
@@ -77149,14 +77149,14 @@
       <c r="E402" s="6" t="n">
         <v>45843.25377314815</v>
       </c>
-      <c r="F402" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G402" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F402" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G402" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H402" s="5" t="inlineStr">
@@ -77340,14 +77340,14 @@
       <c r="E403" s="6" t="n">
         <v>45843.50746527778</v>
       </c>
-      <c r="F403" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G403" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F403" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G403" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
@@ -77531,14 +77531,14 @@
       <c r="E404" s="6" t="n">
         <v>45843.02841435185</v>
       </c>
-      <c r="F404" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G404" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F404" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G404" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H404" s="5" t="inlineStr">
@@ -77722,14 +77722,14 @@
       <c r="E405" s="6" t="n">
         <v>45843.02841435185</v>
       </c>
-      <c r="F405" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G405" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F405" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G405" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H405" s="5" t="inlineStr">
@@ -77913,14 +77913,14 @@
       <c r="E406" s="6" t="n">
         <v>45843.50383101852</v>
       </c>
-      <c r="F406" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G406" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F406" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G406" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H406" s="5" t="inlineStr">
@@ -78104,14 +78104,14 @@
       <c r="E407" s="6" t="n">
         <v>45841.77207175926</v>
       </c>
-      <c r="F407" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G407" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F407" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G407" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H407" s="5" t="inlineStr">
@@ -78295,14 +78295,14 @@
       <c r="E408" s="6" t="n">
         <v>45842.5225</v>
       </c>
-      <c r="F408" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G408" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F408" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G408" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H408" s="5" t="inlineStr">
@@ -78486,14 +78486,14 @@
       <c r="E409" s="6" t="n">
         <v>45842.52256944445</v>
       </c>
-      <c r="F409" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G409" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F409" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G409" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H409" s="5" t="inlineStr">
@@ -78677,14 +78677,14 @@
       <c r="E410" s="6" t="n">
         <v>45845.00399305556</v>
       </c>
-      <c r="F410" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G410" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F410" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G410" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
         </is>
       </c>
       <c r="H410" s="5" t="inlineStr">
@@ -78868,14 +78868,14 @@
       <c r="E411" s="6" t="n">
         <v>45842.54950231482</v>
       </c>
-      <c r="F411" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G411" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F411" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G411" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H411" s="5" t="inlineStr">
@@ -79059,14 +79059,14 @@
       <c r="E412" s="6" t="n">
         <v>45841.80634259259</v>
       </c>
-      <c r="F412" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G412" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F412" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G412" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H412" s="5" t="inlineStr">
@@ -79250,14 +79250,14 @@
       <c r="E413" s="6" t="n">
         <v>45842.79302083333</v>
       </c>
-      <c r="F413" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G413" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F413" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G413" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H413" s="5" t="inlineStr">
@@ -79441,14 +79441,14 @@
       <c r="E414" s="6" t="n">
         <v>45841.80310185185</v>
       </c>
-      <c r="F414" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G414" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F414" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G414" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H414" s="5" t="inlineStr">
@@ -79632,14 +79632,14 @@
       <c r="E415" s="6" t="n">
         <v>45845.0040625</v>
       </c>
-      <c r="F415" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G415" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F415" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G415" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
         </is>
       </c>
       <c r="H415" s="5" t="inlineStr">
@@ -79823,14 +79823,14 @@
       <c r="E416" s="6" t="n">
         <v>45843.50740740741</v>
       </c>
-      <c r="F416" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G416" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F416" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G416" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H416" s="5" t="inlineStr">
@@ -80014,14 +80014,14 @@
       <c r="E417" s="6" t="n">
         <v>45841.77490740741</v>
       </c>
-      <c r="F417" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G417" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F417" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G417" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H417" s="5" t="inlineStr">
